--- a/data/trans_dic/P05A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P05A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,83; 34,58</t>
+          <t>28,82; 34,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 41,47</t>
+          <t>35,05; 41,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,69; 39,71</t>
+          <t>32,83; 39,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 23,1</t>
+          <t>16,43; 22,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 37,05</t>
+          <t>32,09; 37,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,81; 42,39</t>
+          <t>36,65; 42,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,38</t>
+          <t>31,03; 37,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,09</t>
+          <t>16,05; 20,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,19; 35,0</t>
+          <t>31,14; 35,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,02; 41,19</t>
+          <t>36,88; 41,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,68; 37,74</t>
+          <t>32,65; 37,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 20,35</t>
+          <t>16,82; 20,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,06; 29,46</t>
+          <t>25,19; 29,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 41,7</t>
+          <t>37,12; 41,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,63; 36,75</t>
+          <t>32,33; 36,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,49</t>
+          <t>15,39; 19,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,23; 37,09</t>
+          <t>32,45; 37,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 41,56</t>
+          <t>36,73; 41,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,44; 38,8</t>
+          <t>34,38; 38,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 44,05</t>
+          <t>18,52; 21,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,17; 32,45</t>
+          <t>29,21; 32,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,6; 40,92</t>
+          <t>37,57; 40,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 37,16</t>
+          <t>34,2; 37,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 33,23</t>
+          <t>17,34; 19,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,54; 36,68</t>
+          <t>28,79; 36,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,48; 48,61</t>
+          <t>39,31; 49,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 44,44</t>
+          <t>36,12; 44,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,64; 27,27</t>
+          <t>19,04; 26,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,23; 37,74</t>
+          <t>28,99; 37,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 49,23</t>
+          <t>38,98; 48,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 45,37</t>
+          <t>37,23; 45,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,89</t>
+          <t>21,11; 26,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,99; 36,06</t>
+          <t>29,77; 35,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,22; 47,26</t>
+          <t>40,36; 46,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,82; 43,89</t>
+          <t>37,79; 43,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 25,89</t>
+          <t>20,96; 25,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 31,38</t>
+          <t>28,09; 31,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,04; 41,42</t>
+          <t>37,97; 41,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,36; 37,7</t>
+          <t>34,36; 37,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 19,14</t>
+          <t>17,05; 19,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,09</t>
+          <t>32,88; 36,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,05; 41,53</t>
+          <t>38,17; 41,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,07; 38,41</t>
+          <t>35,18; 38,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 37,54</t>
+          <t>19,13; 21,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 33,3</t>
+          <t>30,77; 33,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,47; 41,05</t>
+          <t>38,59; 41,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,21; 37,5</t>
+          <t>35,23; 37,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 30,07</t>
+          <t>18,59; 20,42</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101523</t>
+          <t>111649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>134597</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>236121</t>
+          <t>260720</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>297491; 356810</t>
+          <t>297303; 356537</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>342430; 403686</t>
+          <t>341210; 404616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246562; 299535</t>
+          <t>247689; 300797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85217; 118925</t>
+          <t>95028; 132997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>415530; 487237</t>
+          <t>422031; 491386</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>492046; 566729</t>
+          <t>489938; 566738</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308073; 370918</t>
+          <t>307906; 371426</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>118904; 151749</t>
+          <t>131959; 166641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>731934; 821376</t>
+          <t>730694; 821946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>855200; 951585</t>
+          <t>852125; 953291</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>570882; 659272</t>
+          <t>570316; 654072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>211697; 258495</t>
+          <t>235632; 287997</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>382591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>581688</t>
+          <t>434088</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>923907</t>
+          <t>816680</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>424326; 498854</t>
+          <t>426574; 501106</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>725273; 817537</t>
+          <t>727707; 815261</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>677179; 762703</t>
+          <t>670982; 762137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>235423; 400687</t>
+          <t>343268; 423826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>511701; 588899</t>
+          <t>515273; 592092</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>642529; 728459</t>
+          <t>643797; 729018</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>684780; 771487</t>
+          <t>683649; 770880</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>401533; 985696</t>
+          <t>402124; 471309</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957024; 1064701</t>
+          <t>958277; 1064932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1396304; 1519397</t>
+          <t>1395059; 1520122</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1388852; 1510167</t>
+          <t>1389738; 1516896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>709345; 1504636</t>
+          <t>763219; 870580</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149164</t>
+          <t>158770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>156111</t>
+          <t>174900</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>305275</t>
+          <t>333671</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>157363; 202232</t>
+          <t>158729; 202781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189964; 233925</t>
+          <t>189138; 235934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197247; 243038</t>
+          <t>197555; 245669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126966; 176313</t>
+          <t>135457; 186935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>139263; 179776</t>
+          <t>138120; 179576</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>178810; 225779</t>
+          <t>178763; 221669</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>203523; 249171</t>
+          <t>204424; 247769</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135786; 177206</t>
+          <t>154863; 196042</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>308268; 370604</t>
+          <t>306033; 369168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>378018; 444165</t>
+          <t>379351; 441369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>414553; 481062</t>
+          <t>414137; 477228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>274445; 338079</t>
+          <t>302813; 368402</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592906</t>
+          <t>653010</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>872396</t>
+          <t>758060</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1465302</t>
+          <t>1411071</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>919208; 1028197</t>
+          <t>920308; 1021510</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1299131; 1414561</t>
+          <t>1296621; 1416877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1160109; 1272843</t>
+          <t>1160086; 1273424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>466683; 660714</t>
+          <t>600166; 703398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1107855; 1219558</t>
+          <t>1111094; 1220849</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1350049; 1473815</t>
+          <t>1354515; 1474670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1237743; 1355712</t>
+          <t>1241813; 1354446</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>686178; 1371085</t>
+          <t>712946; 805658</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2057115; 2216172</t>
+          <t>2048095; 2207510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2679065; 2858479</t>
+          <t>2687504; 2860421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2431406; 2590133</t>
+          <t>2433084; 2593301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1260444; 2136042</t>
+          <t>1347450; 1480141</t>
         </is>
       </c>
     </row>
